--- a/Employee_Reports_wi52/Edwin Balakid Tegli Q0157.xlsx
+++ b/Employee_Reports_wi52/Edwin Balakid Tegli Q0157.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFACD"/>
+        <bgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -87,6 +93,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -466,7 +475,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -569,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -584,53 +593,53 @@
       <c r="K3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Storage Retrieval Machine (AMH Trainings)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>AMH</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>LSME-AMH-M-005</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>30-Sep-2024</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>30-Sep-2026</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -667,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -780,151 +789,151 @@
       <c r="K7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Lodige LOTO Procedure (SOPs)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>ELECTRICAL SAFETY</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>LSME-OHS-SOP-021</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>06-Mar-2025</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>06-Mar-2026</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
-        <v>-167</v>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="n">
+        <v>-175</v>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>IMS</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>LSME-IMS-SOP-022</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>29-May-2025</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>29-May-2026</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>-83</v>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="n">
+        <v>-91</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>AMH Sorting Transfer Vehicle Software Recovery Procedure (SOPs)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>AMH</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>LSME-AMH-SOP-002</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>14-Aug-2025</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>14-Aug-2026</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -949,11 +958,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1194,7 +1203,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7612</v>
+        <v>7604</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
